--- a/MortalityExcel.xlsx
+++ b/MortalityExcel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My PC (DESKTOP-JQBDP5S)\Downloads\Mortality Modeling\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My PC (DESKTOP-JQBDP5S)\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0BFCF84-4399-4B5B-8A40-C5D312AA0623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AC4446-569F-4DBA-9FE6-C3961883FD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15915" windowWidth="27960" windowHeight="16440" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="15915" windowWidth="27960" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Female Historical" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,11 @@
     <sheet name="Male Combined Data" sheetId="9" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
   <si>
     <t>Year:</t>
   </si>
@@ -44,18 +43,6 @@
   </si>
   <si>
     <t>P95</t>
-  </si>
-  <si>
-    <t>-32.826</t>
-  </si>
-  <si>
-    <t>-36.877</t>
-  </si>
-  <si>
-    <t>-33.824</t>
-  </si>
-  <si>
-    <t>-39.511</t>
   </si>
   <si>
     <t>P95 Projected</t>
@@ -128,23 +115,17 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
@@ -161,7 +142,13 @@
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
@@ -185,7 +172,7 @@
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3098,11 +3085,11 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="112"/>
-                <c:pt idx="92" formatCode="#,##0.000;[Red]\-#,##0.000">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="93" formatCode="#,##0.000;[Red]\-#,##0.000">
-                  <c:v>0</c:v>
+                <c:pt idx="92">
+                  <c:v>-32.826000000000001</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>-33.823999999999998</c:v>
                 </c:pt>
                 <c:pt idx="94" formatCode="#,##0.000;[Red]\-#,##0.000">
                   <c:v>-34.963555136438501</c:v>
@@ -3545,11 +3532,11 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="112"/>
-                <c:pt idx="92" formatCode="#,##0.000;[Red]\-#,##0.000">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="93" formatCode="#,##0.000;[Red]\-#,##0.000">
-                  <c:v>0</c:v>
+                <c:pt idx="92">
+                  <c:v>-36.877000000000002</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>-39.511000000000003</c:v>
                 </c:pt>
                 <c:pt idx="94" formatCode="#,##0.000;[Red]\-#,##0.000">
                   <c:v>-41.803730678080541</c:v>
@@ -11857,8 +11844,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{195649B8-8D0B-4522-AC0C-8B85A3A56063}" name="Frame07" displayName="Frame07" ref="A1:E93" totalsRowShown="0">
   <autoFilter ref="A1:E93" xr:uid="{195649B8-8D0B-4522-AC0C-8B85A3A56063}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D452DDE8-2CF6-446E-A4F9-D820195B59F3}" name="Year:" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{D2BFA669-97B8-4863-8EEB-2DC0D54A1BEB}" name="Historical" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{D452DDE8-2CF6-446E-A4F9-D820195B59F3}" name="Year:" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{D2BFA669-97B8-4863-8EEB-2DC0D54A1BEB}" name="Historical" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{A4410D91-46C3-4933-93B9-3589CE6C5ED0}" name="Median"/>
     <tableColumn id="4" xr3:uid="{A212DB55-74B7-4C6F-8DE9-7F64D74C8FED}" name="P05 Projected"/>
     <tableColumn id="5" xr3:uid="{7371A724-730E-4956-918D-7F6EDD168182}" name="P95 Projected"/>
@@ -11871,8 +11858,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Frame1" displayName="Frame1" ref="A1:B93" totalsRowShown="0">
   <autoFilter ref="A1:B93" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Year:" dataDxfId="0"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="k_t" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Year:" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="k_t" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11882,10 +11869,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Frame3" displayName="Frame3" ref="A1:D21" totalsRowShown="0">
   <autoFilter ref="A1:D21" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Year" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Median" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="P05" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="P95" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Year" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Median" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="P05" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="P95" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11895,8 +11882,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4EA9706A-B69C-47D9-9690-9C84BF1310FE}" name="Frame16" displayName="Frame16" ref="A1:E113" totalsRowShown="0">
   <autoFilter ref="A1:E113" xr:uid="{4EA9706A-B69C-47D9-9690-9C84BF1310FE}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D07CE5DA-38CC-49B0-96AB-D0E068147ED1}" name="Year:" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{9435D52C-767A-4344-B263-9120546BB3B8}" name="k_t" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{D07CE5DA-38CC-49B0-96AB-D0E068147ED1}" name="Year:" dataDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{9435D52C-767A-4344-B263-9120546BB3B8}" name="k_t" dataDxfId="0"/>
     <tableColumn id="3" xr3:uid="{6A3D2032-395C-48B2-A9EA-099822BEC295}" name="Median"/>
     <tableColumn id="4" xr3:uid="{9DBE78B3-F18E-4191-927C-293EE033DF1B}" name="P05 Projected"/>
     <tableColumn id="5" xr3:uid="{EFFE7BB2-FD43-4DAD-A6B0-317962C2BC1A}" name="P95 Projected"/>
@@ -13266,16 +13253,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
@@ -14018,11 +14005,11 @@
       <c r="A94" s="6">
         <v>2025</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>7</v>
+      <c r="C94" s="9">
+        <v>-32.826000000000001</v>
+      </c>
+      <c r="D94" s="9">
+        <v>-36.877000000000002</v>
       </c>
       <c r="E94" s="2">
         <v>-28.721854136666511</v>
@@ -14032,11 +14019,11 @@
       <c r="A95" s="6">
         <v>2026</v>
       </c>
-      <c r="C95" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="8" t="s">
-        <v>9</v>
+      <c r="C95" s="9">
+        <v>-33.823999999999998</v>
+      </c>
+      <c r="D95" s="9">
+        <v>-39.511000000000003</v>
       </c>
       <c r="E95" s="2">
         <v>-28.189225283400098</v>
@@ -14345,7 +14332,7 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>1933</v>
       </c>
       <c r="B2" s="2">
@@ -14353,7 +14340,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1934</v>
       </c>
       <c r="B3" s="2">
@@ -14361,7 +14348,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>1935</v>
       </c>
       <c r="B4" s="2">
@@ -14369,7 +14356,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>1936</v>
       </c>
       <c r="B5" s="2">
@@ -14377,7 +14364,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>1937</v>
       </c>
       <c r="B6" s="2">
@@ -14385,7 +14372,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>1938</v>
       </c>
       <c r="B7" s="2">
@@ -14393,7 +14380,7 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>1939</v>
       </c>
       <c r="B8" s="2">
@@ -14401,7 +14388,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>1940</v>
       </c>
       <c r="B9" s="2">
@@ -14409,7 +14396,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>1941</v>
       </c>
       <c r="B10" s="2">
@@ -14417,7 +14404,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>1942</v>
       </c>
       <c r="B11" s="2">
@@ -14425,7 +14412,7 @@
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>1943</v>
       </c>
       <c r="B12" s="2">
@@ -14433,7 +14420,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>1944</v>
       </c>
       <c r="B13" s="2">
@@ -14441,7 +14428,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>1945</v>
       </c>
       <c r="B14" s="2">
@@ -14449,7 +14436,7 @@
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>1946</v>
       </c>
       <c r="B15" s="2">
@@ -14457,7 +14444,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>1947</v>
       </c>
       <c r="B16" s="2">
@@ -14465,7 +14452,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>1948</v>
       </c>
       <c r="B17" s="2">
@@ -14473,7 +14460,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>1949</v>
       </c>
       <c r="B18" s="2">
@@ -14481,7 +14468,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="9">
+      <c r="A19" s="8">
         <v>1950</v>
       </c>
       <c r="B19" s="2">
@@ -14489,7 +14476,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="9">
+      <c r="A20" s="8">
         <v>1951</v>
       </c>
       <c r="B20" s="2">
@@ -14497,7 +14484,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>1952</v>
       </c>
       <c r="B21" s="2">
@@ -14505,7 +14492,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="9">
+      <c r="A22" s="8">
         <v>1953</v>
       </c>
       <c r="B22" s="2">
@@ -14513,7 +14500,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="9">
+      <c r="A23" s="8">
         <v>1954</v>
       </c>
       <c r="B23" s="2">
@@ -14521,7 +14508,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="9">
+      <c r="A24" s="8">
         <v>1955</v>
       </c>
       <c r="B24" s="2">
@@ -14529,7 +14516,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="9">
+      <c r="A25" s="8">
         <v>1956</v>
       </c>
       <c r="B25" s="2">
@@ -14537,7 +14524,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="9">
+      <c r="A26" s="8">
         <v>1957</v>
       </c>
       <c r="B26" s="2">
@@ -14545,7 +14532,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="9">
+      <c r="A27" s="8">
         <v>1958</v>
       </c>
       <c r="B27" s="2">
@@ -14553,7 +14540,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="9">
+      <c r="A28" s="8">
         <v>1959</v>
       </c>
       <c r="B28" s="2">
@@ -14561,7 +14548,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="9">
+      <c r="A29" s="8">
         <v>1960</v>
       </c>
       <c r="B29" s="2">
@@ -14569,7 +14556,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="9">
+      <c r="A30" s="8">
         <v>1961</v>
       </c>
       <c r="B30" s="2">
@@ -14577,7 +14564,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="9">
+      <c r="A31" s="8">
         <v>1962</v>
       </c>
       <c r="B31" s="2">
@@ -14585,7 +14572,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="9">
+      <c r="A32" s="8">
         <v>1963</v>
       </c>
       <c r="B32" s="2">
@@ -14593,7 +14580,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="9">
+      <c r="A33" s="8">
         <v>1964</v>
       </c>
       <c r="B33" s="2">
@@ -14601,7 +14588,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="9">
+      <c r="A34" s="8">
         <v>1965</v>
       </c>
       <c r="B34" s="2">
@@ -14609,7 +14596,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="9">
+      <c r="A35" s="8">
         <v>1966</v>
       </c>
       <c r="B35" s="2">
@@ -14617,7 +14604,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="9">
+      <c r="A36" s="8">
         <v>1967</v>
       </c>
       <c r="B36" s="2">
@@ -14625,7 +14612,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="9">
+      <c r="A37" s="8">
         <v>1968</v>
       </c>
       <c r="B37" s="2">
@@ -14633,7 +14620,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="9">
+      <c r="A38" s="8">
         <v>1969</v>
       </c>
       <c r="B38" s="2">
@@ -14641,7 +14628,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="9">
+      <c r="A39" s="8">
         <v>1970</v>
       </c>
       <c r="B39" s="2">
@@ -14649,7 +14636,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="9">
+      <c r="A40" s="8">
         <v>1971</v>
       </c>
       <c r="B40" s="2">
@@ -14657,7 +14644,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="9">
+      <c r="A41" s="8">
         <v>1972</v>
       </c>
       <c r="B41" s="2">
@@ -14665,7 +14652,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="9">
+      <c r="A42" s="8">
         <v>1973</v>
       </c>
       <c r="B42" s="2">
@@ -14673,7 +14660,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="9">
+      <c r="A43" s="8">
         <v>1974</v>
       </c>
       <c r="B43" s="2">
@@ -14681,7 +14668,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="9">
+      <c r="A44" s="8">
         <v>1975</v>
       </c>
       <c r="B44" s="2">
@@ -14689,7 +14676,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="9">
+      <c r="A45" s="8">
         <v>1976</v>
       </c>
       <c r="B45" s="2">
@@ -14697,7 +14684,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="9">
+      <c r="A46" s="8">
         <v>1977</v>
       </c>
       <c r="B46" s="2">
@@ -14705,7 +14692,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="9">
+      <c r="A47" s="8">
         <v>1978</v>
       </c>
       <c r="B47" s="2">
@@ -14713,7 +14700,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="9">
+      <c r="A48" s="8">
         <v>1979</v>
       </c>
       <c r="B48" s="2">
@@ -14721,7 +14708,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="9">
+      <c r="A49" s="8">
         <v>1980</v>
       </c>
       <c r="B49" s="2">
@@ -14729,7 +14716,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="9">
+      <c r="A50" s="8">
         <v>1981</v>
       </c>
       <c r="B50" s="2">
@@ -14737,7 +14724,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="9">
+      <c r="A51" s="8">
         <v>1982</v>
       </c>
       <c r="B51" s="2">
@@ -14745,7 +14732,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="9">
+      <c r="A52" s="8">
         <v>1983</v>
       </c>
       <c r="B52" s="2">
@@ -14753,7 +14740,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="9">
+      <c r="A53" s="8">
         <v>1984</v>
       </c>
       <c r="B53" s="2">
@@ -14761,7 +14748,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="9">
+      <c r="A54" s="8">
         <v>1985</v>
       </c>
       <c r="B54" s="2">
@@ -14769,7 +14756,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="9">
+      <c r="A55" s="8">
         <v>1986</v>
       </c>
       <c r="B55" s="2">
@@ -14777,7 +14764,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="9">
+      <c r="A56" s="8">
         <v>1987</v>
       </c>
       <c r="B56" s="2">
@@ -14785,7 +14772,7 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="9">
+      <c r="A57" s="8">
         <v>1988</v>
       </c>
       <c r="B57" s="2">
@@ -14793,7 +14780,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="9">
+      <c r="A58" s="8">
         <v>1989</v>
       </c>
       <c r="B58" s="2">
@@ -14801,7 +14788,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="9">
+      <c r="A59" s="8">
         <v>1990</v>
       </c>
       <c r="B59" s="2">
@@ -14809,7 +14796,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="9">
+      <c r="A60" s="8">
         <v>1991</v>
       </c>
       <c r="B60" s="2">
@@ -14817,7 +14804,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="9">
+      <c r="A61" s="8">
         <v>1992</v>
       </c>
       <c r="B61" s="2">
@@ -14825,7 +14812,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="9">
+      <c r="A62" s="8">
         <v>1993</v>
       </c>
       <c r="B62" s="2">
@@ -14833,7 +14820,7 @@
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="9">
+      <c r="A63" s="8">
         <v>1994</v>
       </c>
       <c r="B63" s="2">
@@ -14841,7 +14828,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="9">
+      <c r="A64" s="8">
         <v>1995</v>
       </c>
       <c r="B64" s="2">
@@ -14849,7 +14836,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="9">
+      <c r="A65" s="8">
         <v>1996</v>
       </c>
       <c r="B65" s="2">
@@ -14857,7 +14844,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="9">
+      <c r="A66" s="8">
         <v>1997</v>
       </c>
       <c r="B66" s="2">
@@ -14865,7 +14852,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="9">
+      <c r="A67" s="8">
         <v>1998</v>
       </c>
       <c r="B67" s="2">
@@ -14873,7 +14860,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="9">
+      <c r="A68" s="8">
         <v>1999</v>
       </c>
       <c r="B68" s="2">
@@ -14881,7 +14868,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="9">
+      <c r="A69" s="8">
         <v>2000</v>
       </c>
       <c r="B69" s="2">
@@ -14889,7 +14876,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="9">
+      <c r="A70" s="8">
         <v>2001</v>
       </c>
       <c r="B70" s="2">
@@ -14897,7 +14884,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="9">
+      <c r="A71" s="8">
         <v>2002</v>
       </c>
       <c r="B71" s="2">
@@ -14905,7 +14892,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="9">
+      <c r="A72" s="8">
         <v>2003</v>
       </c>
       <c r="B72" s="2">
@@ -14913,7 +14900,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="9">
+      <c r="A73" s="8">
         <v>2004</v>
       </c>
       <c r="B73" s="2">
@@ -14921,7 +14908,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="9">
+      <c r="A74" s="8">
         <v>2005</v>
       </c>
       <c r="B74" s="2">
@@ -14929,7 +14916,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="9">
+      <c r="A75" s="8">
         <v>2006</v>
       </c>
       <c r="B75" s="2">
@@ -14937,7 +14924,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="9">
+      <c r="A76" s="8">
         <v>2007</v>
       </c>
       <c r="B76" s="2">
@@ -14945,7 +14932,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="9">
+      <c r="A77" s="8">
         <v>2008</v>
       </c>
       <c r="B77" s="2">
@@ -14953,7 +14940,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="9">
+      <c r="A78" s="8">
         <v>2009</v>
       </c>
       <c r="B78" s="2">
@@ -14961,7 +14948,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="9">
+      <c r="A79" s="8">
         <v>2010</v>
       </c>
       <c r="B79" s="2">
@@ -14969,7 +14956,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="9">
+      <c r="A80" s="8">
         <v>2011</v>
       </c>
       <c r="B80" s="2">
@@ -14977,7 +14964,7 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A81" s="9">
+      <c r="A81" s="8">
         <v>2012</v>
       </c>
       <c r="B81" s="2">
@@ -14985,7 +14972,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A82" s="9">
+      <c r="A82" s="8">
         <v>2013</v>
       </c>
       <c r="B82" s="2">
@@ -14993,7 +14980,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A83" s="9">
+      <c r="A83" s="8">
         <v>2014</v>
       </c>
       <c r="B83" s="2">
@@ -15001,7 +14988,7 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A84" s="9">
+      <c r="A84" s="8">
         <v>2015</v>
       </c>
       <c r="B84" s="2">
@@ -15009,7 +14996,7 @@
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A85" s="9">
+      <c r="A85" s="8">
         <v>2016</v>
       </c>
       <c r="B85" s="2">
@@ -15017,7 +15004,7 @@
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A86" s="9">
+      <c r="A86" s="8">
         <v>2017</v>
       </c>
       <c r="B86" s="2">
@@ -15025,7 +15012,7 @@
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A87" s="9">
+      <c r="A87" s="8">
         <v>2018</v>
       </c>
       <c r="B87" s="2">
@@ -15033,7 +15020,7 @@
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A88" s="9">
+      <c r="A88" s="8">
         <v>2019</v>
       </c>
       <c r="B88" s="2">
@@ -15041,7 +15028,7 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A89" s="9">
+      <c r="A89" s="8">
         <v>2020</v>
       </c>
       <c r="B89" s="2">
@@ -15049,7 +15036,7 @@
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A90" s="9">
+      <c r="A90" s="8">
         <v>2021</v>
       </c>
       <c r="B90" s="2">
@@ -15057,7 +15044,7 @@
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A91" s="9">
+      <c r="A91" s="8">
         <v>2022</v>
       </c>
       <c r="B91" s="2">
@@ -15065,7 +15052,7 @@
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A92" s="9">
+      <c r="A92" s="8">
         <v>2023</v>
       </c>
       <c r="B92" s="2">
@@ -15073,7 +15060,7 @@
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A93" s="9">
+      <c r="A93" s="8">
         <v>2024</v>
       </c>
       <c r="B93" s="2">
@@ -15109,7 +15096,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>2025</v>
       </c>
       <c r="B2" s="2">
@@ -15123,7 +15110,7 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>2026</v>
       </c>
       <c r="B3" s="2">
@@ -15137,7 +15124,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>2027</v>
       </c>
       <c r="B4" s="2">
@@ -15151,7 +15138,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>2028</v>
       </c>
       <c r="B5" s="2">
@@ -15165,7 +15152,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>2029</v>
       </c>
       <c r="B6" s="2">
@@ -15179,7 +15166,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>2030</v>
       </c>
       <c r="B7" s="2">
@@ -15193,7 +15180,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>2031</v>
       </c>
       <c r="B8" s="2">
@@ -15207,7 +15194,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>2032</v>
       </c>
       <c r="B9" s="2">
@@ -15221,7 +15208,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>2033</v>
       </c>
       <c r="B10" s="2">
@@ -15235,7 +15222,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>2034</v>
       </c>
       <c r="B11" s="2">
@@ -15249,7 +15236,7 @@
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>2035</v>
       </c>
       <c r="B12" s="2">
@@ -15263,7 +15250,7 @@
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>2036</v>
       </c>
       <c r="B13" s="2">
@@ -15277,7 +15264,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>2037</v>
       </c>
       <c r="B14" s="2">
@@ -15291,7 +15278,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>2038</v>
       </c>
       <c r="B15" s="2">
@@ -15305,7 +15292,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>2039</v>
       </c>
       <c r="B16" s="2">
@@ -15319,7 +15306,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>2040</v>
       </c>
       <c r="B17" s="2">
@@ -15333,7 +15320,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>2041</v>
       </c>
       <c r="B18" s="2">
@@ -15347,7 +15334,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="9">
+      <c r="A19" s="8">
         <v>2042</v>
       </c>
       <c r="B19" s="2">
@@ -15361,7 +15348,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="9">
+      <c r="A20" s="8">
         <v>2043</v>
       </c>
       <c r="B20" s="2">
@@ -15375,7 +15362,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>2044</v>
       </c>
       <c r="B21" s="2">
@@ -15413,14 +15400,14 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+      <c r="A2" s="8">
         <v>1933</v>
       </c>
       <c r="B2" s="2">
@@ -15428,7 +15415,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="9">
+      <c r="A3" s="8">
         <v>1934</v>
       </c>
       <c r="B3" s="2">
@@ -15436,7 +15423,7 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>1935</v>
       </c>
       <c r="B4" s="2">
@@ -15444,7 +15431,7 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="9">
+      <c r="A5" s="8">
         <v>1936</v>
       </c>
       <c r="B5" s="2">
@@ -15452,7 +15439,7 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="9">
+      <c r="A6" s="8">
         <v>1937</v>
       </c>
       <c r="B6" s="2">
@@ -15460,7 +15447,7 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="9">
+      <c r="A7" s="8">
         <v>1938</v>
       </c>
       <c r="B7" s="2">
@@ -15468,7 +15455,7 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="9">
+      <c r="A8" s="8">
         <v>1939</v>
       </c>
       <c r="B8" s="2">
@@ -15476,7 +15463,7 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="9">
+      <c r="A9" s="8">
         <v>1940</v>
       </c>
       <c r="B9" s="2">
@@ -15484,7 +15471,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="9">
+      <c r="A10" s="8">
         <v>1941</v>
       </c>
       <c r="B10" s="2">
@@ -15492,7 +15479,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="9">
+      <c r="A11" s="8">
         <v>1942</v>
       </c>
       <c r="B11" s="2">
@@ -15500,7 +15487,7 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="9">
+      <c r="A12" s="8">
         <v>1943</v>
       </c>
       <c r="B12" s="2">
@@ -15508,7 +15495,7 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="9">
+      <c r="A13" s="8">
         <v>1944</v>
       </c>
       <c r="B13" s="2">
@@ -15516,7 +15503,7 @@
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="9">
+      <c r="A14" s="8">
         <v>1945</v>
       </c>
       <c r="B14" s="2">
@@ -15524,7 +15511,7 @@
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="9">
+      <c r="A15" s="8">
         <v>1946</v>
       </c>
       <c r="B15" s="2">
@@ -15532,7 +15519,7 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="9">
+      <c r="A16" s="8">
         <v>1947</v>
       </c>
       <c r="B16" s="2">
@@ -15540,7 +15527,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="9">
+      <c r="A17" s="8">
         <v>1948</v>
       </c>
       <c r="B17" s="2">
@@ -15548,7 +15535,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" s="9">
+      <c r="A18" s="8">
         <v>1949</v>
       </c>
       <c r="B18" s="2">
@@ -15556,7 +15543,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" s="9">
+      <c r="A19" s="8">
         <v>1950</v>
       </c>
       <c r="B19" s="2">
@@ -15564,7 +15551,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20" s="9">
+      <c r="A20" s="8">
         <v>1951</v>
       </c>
       <c r="B20" s="2">
@@ -15572,7 +15559,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A21" s="9">
+      <c r="A21" s="8">
         <v>1952</v>
       </c>
       <c r="B21" s="2">
@@ -15580,7 +15567,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" s="9">
+      <c r="A22" s="8">
         <v>1953</v>
       </c>
       <c r="B22" s="2">
@@ -15588,7 +15575,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A23" s="9">
+      <c r="A23" s="8">
         <v>1954</v>
       </c>
       <c r="B23" s="2">
@@ -15596,7 +15583,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A24" s="9">
+      <c r="A24" s="8">
         <v>1955</v>
       </c>
       <c r="B24" s="2">
@@ -15604,7 +15591,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="9">
+      <c r="A25" s="8">
         <v>1956</v>
       </c>
       <c r="B25" s="2">
@@ -15612,7 +15599,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A26" s="9">
+      <c r="A26" s="8">
         <v>1957</v>
       </c>
       <c r="B26" s="2">
@@ -15620,7 +15607,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A27" s="9">
+      <c r="A27" s="8">
         <v>1958</v>
       </c>
       <c r="B27" s="2">
@@ -15628,7 +15615,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A28" s="9">
+      <c r="A28" s="8">
         <v>1959</v>
       </c>
       <c r="B28" s="2">
@@ -15636,7 +15623,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A29" s="9">
+      <c r="A29" s="8">
         <v>1960</v>
       </c>
       <c r="B29" s="2">
@@ -15644,7 +15631,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A30" s="9">
+      <c r="A30" s="8">
         <v>1961</v>
       </c>
       <c r="B30" s="2">
@@ -15652,7 +15639,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A31" s="9">
+      <c r="A31" s="8">
         <v>1962</v>
       </c>
       <c r="B31" s="2">
@@ -15660,7 +15647,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A32" s="9">
+      <c r="A32" s="8">
         <v>1963</v>
       </c>
       <c r="B32" s="2">
@@ -15668,7 +15655,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A33" s="9">
+      <c r="A33" s="8">
         <v>1964</v>
       </c>
       <c r="B33" s="2">
@@ -15676,7 +15663,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A34" s="9">
+      <c r="A34" s="8">
         <v>1965</v>
       </c>
       <c r="B34" s="2">
@@ -15684,7 +15671,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A35" s="9">
+      <c r="A35" s="8">
         <v>1966</v>
       </c>
       <c r="B35" s="2">
@@ -15692,7 +15679,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A36" s="9">
+      <c r="A36" s="8">
         <v>1967</v>
       </c>
       <c r="B36" s="2">
@@ -15700,7 +15687,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A37" s="9">
+      <c r="A37" s="8">
         <v>1968</v>
       </c>
       <c r="B37" s="2">
@@ -15708,7 +15695,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A38" s="9">
+      <c r="A38" s="8">
         <v>1969</v>
       </c>
       <c r="B38" s="2">
@@ -15716,7 +15703,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A39" s="9">
+      <c r="A39" s="8">
         <v>1970</v>
       </c>
       <c r="B39" s="2">
@@ -15724,7 +15711,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A40" s="9">
+      <c r="A40" s="8">
         <v>1971</v>
       </c>
       <c r="B40" s="2">
@@ -15732,7 +15719,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A41" s="9">
+      <c r="A41" s="8">
         <v>1972</v>
       </c>
       <c r="B41" s="2">
@@ -15740,7 +15727,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A42" s="9">
+      <c r="A42" s="8">
         <v>1973</v>
       </c>
       <c r="B42" s="2">
@@ -15748,7 +15735,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A43" s="9">
+      <c r="A43" s="8">
         <v>1974</v>
       </c>
       <c r="B43" s="2">
@@ -15756,7 +15743,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A44" s="9">
+      <c r="A44" s="8">
         <v>1975</v>
       </c>
       <c r="B44" s="2">
@@ -15764,7 +15751,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A45" s="9">
+      <c r="A45" s="8">
         <v>1976</v>
       </c>
       <c r="B45" s="2">
@@ -15772,7 +15759,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A46" s="9">
+      <c r="A46" s="8">
         <v>1977</v>
       </c>
       <c r="B46" s="2">
@@ -15780,7 +15767,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A47" s="9">
+      <c r="A47" s="8">
         <v>1978</v>
       </c>
       <c r="B47" s="2">
@@ -15788,7 +15775,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" s="9">
+      <c r="A48" s="8">
         <v>1979</v>
       </c>
       <c r="B48" s="2">
@@ -15796,7 +15783,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A49" s="9">
+      <c r="A49" s="8">
         <v>1980</v>
       </c>
       <c r="B49" s="2">
@@ -15804,7 +15791,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A50" s="9">
+      <c r="A50" s="8">
         <v>1981</v>
       </c>
       <c r="B50" s="2">
@@ -15812,7 +15799,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A51" s="9">
+      <c r="A51" s="8">
         <v>1982</v>
       </c>
       <c r="B51" s="2">
@@ -15820,7 +15807,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A52" s="9">
+      <c r="A52" s="8">
         <v>1983</v>
       </c>
       <c r="B52" s="2">
@@ -15828,7 +15815,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A53" s="9">
+      <c r="A53" s="8">
         <v>1984</v>
       </c>
       <c r="B53" s="2">
@@ -15836,7 +15823,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A54" s="9">
+      <c r="A54" s="8">
         <v>1985</v>
       </c>
       <c r="B54" s="2">
@@ -15844,7 +15831,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A55" s="9">
+      <c r="A55" s="8">
         <v>1986</v>
       </c>
       <c r="B55" s="2">
@@ -15852,7 +15839,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A56" s="9">
+      <c r="A56" s="8">
         <v>1987</v>
       </c>
       <c r="B56" s="2">
@@ -15860,7 +15847,7 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A57" s="9">
+      <c r="A57" s="8">
         <v>1988</v>
       </c>
       <c r="B57" s="2">
@@ -15868,7 +15855,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A58" s="9">
+      <c r="A58" s="8">
         <v>1989</v>
       </c>
       <c r="B58" s="2">
@@ -15876,7 +15863,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A59" s="9">
+      <c r="A59" s="8">
         <v>1990</v>
       </c>
       <c r="B59" s="2">
@@ -15884,7 +15871,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A60" s="9">
+      <c r="A60" s="8">
         <v>1991</v>
       </c>
       <c r="B60" s="2">
@@ -15892,7 +15879,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A61" s="9">
+      <c r="A61" s="8">
         <v>1992</v>
       </c>
       <c r="B61" s="2">
@@ -15900,7 +15887,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="9">
+      <c r="A62" s="8">
         <v>1993</v>
       </c>
       <c r="B62" s="2">
@@ -15908,7 +15895,7 @@
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" s="9">
+      <c r="A63" s="8">
         <v>1994</v>
       </c>
       <c r="B63" s="2">
@@ -15916,7 +15903,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" s="9">
+      <c r="A64" s="8">
         <v>1995</v>
       </c>
       <c r="B64" s="2">
@@ -15924,7 +15911,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A65" s="9">
+      <c r="A65" s="8">
         <v>1996</v>
       </c>
       <c r="B65" s="2">
@@ -15932,7 +15919,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A66" s="9">
+      <c r="A66" s="8">
         <v>1997</v>
       </c>
       <c r="B66" s="2">
@@ -15940,7 +15927,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A67" s="9">
+      <c r="A67" s="8">
         <v>1998</v>
       </c>
       <c r="B67" s="2">
@@ -15948,7 +15935,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A68" s="9">
+      <c r="A68" s="8">
         <v>1999</v>
       </c>
       <c r="B68" s="2">
@@ -15956,7 +15943,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A69" s="9">
+      <c r="A69" s="8">
         <v>2000</v>
       </c>
       <c r="B69" s="2">
@@ -15964,7 +15951,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A70" s="9">
+      <c r="A70" s="8">
         <v>2001</v>
       </c>
       <c r="B70" s="2">
@@ -15972,7 +15959,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A71" s="9">
+      <c r="A71" s="8">
         <v>2002</v>
       </c>
       <c r="B71" s="2">
@@ -15980,7 +15967,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A72" s="9">
+      <c r="A72" s="8">
         <v>2003</v>
       </c>
       <c r="B72" s="2">
@@ -15988,7 +15975,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A73" s="9">
+      <c r="A73" s="8">
         <v>2004</v>
       </c>
       <c r="B73" s="2">
@@ -15996,7 +15983,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A74" s="9">
+      <c r="A74" s="8">
         <v>2005</v>
       </c>
       <c r="B74" s="2">
@@ -16004,7 +15991,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A75" s="9">
+      <c r="A75" s="8">
         <v>2006</v>
       </c>
       <c r="B75" s="2">
@@ -16012,7 +15999,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A76" s="9">
+      <c r="A76" s="8">
         <v>2007</v>
       </c>
       <c r="B76" s="2">
@@ -16020,7 +16007,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A77" s="9">
+      <c r="A77" s="8">
         <v>2008</v>
       </c>
       <c r="B77" s="2">
@@ -16028,7 +16015,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A78" s="9">
+      <c r="A78" s="8">
         <v>2009</v>
       </c>
       <c r="B78" s="2">
@@ -16036,7 +16023,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A79" s="9">
+      <c r="A79" s="8">
         <v>2010</v>
       </c>
       <c r="B79" s="2">
@@ -16044,7 +16031,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A80" s="9">
+      <c r="A80" s="8">
         <v>2011</v>
       </c>
       <c r="B80" s="2">
@@ -16052,7 +16039,7 @@
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="9">
+      <c r="A81" s="8">
         <v>2012</v>
       </c>
       <c r="B81" s="2">
@@ -16060,7 +16047,7 @@
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="9">
+      <c r="A82" s="8">
         <v>2013</v>
       </c>
       <c r="B82" s="2">
@@ -16068,7 +16055,7 @@
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" s="9">
+      <c r="A83" s="8">
         <v>2014</v>
       </c>
       <c r="B83" s="2">
@@ -16076,7 +16063,7 @@
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="9">
+      <c r="A84" s="8">
         <v>2015</v>
       </c>
       <c r="B84" s="2">
@@ -16084,7 +16071,7 @@
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="9">
+      <c r="A85" s="8">
         <v>2016</v>
       </c>
       <c r="B85" s="2">
@@ -16092,7 +16079,7 @@
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="9">
+      <c r="A86" s="8">
         <v>2017</v>
       </c>
       <c r="B86" s="2">
@@ -16100,7 +16087,7 @@
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="9">
+      <c r="A87" s="8">
         <v>2018</v>
       </c>
       <c r="B87" s="2">
@@ -16108,7 +16095,7 @@
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="9">
+      <c r="A88" s="8">
         <v>2019</v>
       </c>
       <c r="B88" s="2">
@@ -16116,7 +16103,7 @@
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="9">
+      <c r="A89" s="8">
         <v>2020</v>
       </c>
       <c r="B89" s="2">
@@ -16124,7 +16111,7 @@
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="9">
+      <c r="A90" s="8">
         <v>2021</v>
       </c>
       <c r="B90" s="2">
@@ -16132,7 +16119,7 @@
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="9">
+      <c r="A91" s="8">
         <v>2022</v>
       </c>
       <c r="B91" s="2">
@@ -16140,7 +16127,7 @@
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="9">
+      <c r="A92" s="8">
         <v>2023</v>
       </c>
       <c r="B92" s="2">
@@ -16148,7 +16135,7 @@
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="9">
+      <c r="A93" s="8">
         <v>2024</v>
       </c>
       <c r="B93" s="2">
@@ -16156,7 +16143,7 @@
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="9">
+      <c r="A94" s="8">
         <v>2025</v>
       </c>
       <c r="B94" s="7"/>
@@ -16171,7 +16158,7 @@
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="9">
+      <c r="A95" s="8">
         <v>2026</v>
       </c>
       <c r="B95" s="7"/>
@@ -16186,7 +16173,7 @@
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="9">
+      <c r="A96" s="8">
         <v>2027</v>
       </c>
       <c r="B96" s="7"/>
@@ -16201,7 +16188,7 @@
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="9">
+      <c r="A97" s="8">
         <v>2028</v>
       </c>
       <c r="B97" s="7"/>
@@ -16216,7 +16203,7 @@
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="9">
+      <c r="A98" s="8">
         <v>2029</v>
       </c>
       <c r="B98" s="7"/>
@@ -16231,7 +16218,7 @@
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A99" s="9">
+      <c r="A99" s="8">
         <v>2030</v>
       </c>
       <c r="B99" s="7"/>
@@ -16246,7 +16233,7 @@
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="9">
+      <c r="A100" s="8">
         <v>2031</v>
       </c>
       <c r="B100" s="7"/>
@@ -16261,7 +16248,7 @@
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="9">
+      <c r="A101" s="8">
         <v>2032</v>
       </c>
       <c r="B101" s="7"/>
@@ -16276,7 +16263,7 @@
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A102" s="9">
+      <c r="A102" s="8">
         <v>2033</v>
       </c>
       <c r="B102" s="7"/>
@@ -16291,7 +16278,7 @@
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A103" s="9">
+      <c r="A103" s="8">
         <v>2034</v>
       </c>
       <c r="B103" s="7"/>
@@ -16306,7 +16293,7 @@
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A104" s="9">
+      <c r="A104" s="8">
         <v>2035</v>
       </c>
       <c r="B104" s="7"/>
@@ -16321,7 +16308,7 @@
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A105" s="9">
+      <c r="A105" s="8">
         <v>2036</v>
       </c>
       <c r="B105" s="7"/>
@@ -16336,7 +16323,7 @@
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="9">
+      <c r="A106" s="8">
         <v>2037</v>
       </c>
       <c r="B106" s="7"/>
@@ -16351,7 +16338,7 @@
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A107" s="9">
+      <c r="A107" s="8">
         <v>2038</v>
       </c>
       <c r="B107" s="7"/>
@@ -16366,7 +16353,7 @@
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A108" s="9">
+      <c r="A108" s="8">
         <v>2039</v>
       </c>
       <c r="B108" s="7"/>
@@ -16381,7 +16368,7 @@
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" s="9">
+      <c r="A109" s="8">
         <v>2040</v>
       </c>
       <c r="B109" s="7"/>
@@ -16396,7 +16383,7 @@
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110" s="9">
+      <c r="A110" s="8">
         <v>2041</v>
       </c>
       <c r="B110" s="7"/>
@@ -16411,7 +16398,7 @@
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" s="9">
+      <c r="A111" s="8">
         <v>2042</v>
       </c>
       <c r="B111" s="7"/>
@@ -16426,7 +16413,7 @@
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" s="9">
+      <c r="A112" s="8">
         <v>2043</v>
       </c>
       <c r="B112" s="7"/>
@@ -16441,7 +16428,7 @@
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A113" s="9">
+      <c r="A113" s="8">
         <v>2044</v>
       </c>
       <c r="B113" s="7"/>

--- a/MortalityExcel.xlsx
+++ b/MortalityExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My PC (DESKTOP-JQBDP5S)\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AC4446-569F-4DBA-9FE6-C3961883FD1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB71CA2-B701-48F7-8C4D-3B0E12787AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15915" windowWidth="27960" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="15915" windowWidth="27960" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Female Historical" sheetId="1" r:id="rId1"/>
@@ -154,6 +154,12 @@
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
     <dxf>
@@ -167,12 +173,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -11820,8 +11820,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Frame0" displayName="Frame0" ref="A1:B93" totalsRowShown="0">
   <autoFilter ref="A1:B93" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year:" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="k_t" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year:" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="k_t" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11831,10 +11831,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Frame2" displayName="Frame2" ref="A1:D21" totalsRowShown="0">
   <autoFilter ref="A1:D21" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Year" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Median" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="P05" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="P95" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Year" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Median" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="P05" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="P95" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11844,8 +11844,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{195649B8-8D0B-4522-AC0C-8B85A3A56063}" name="Frame07" displayName="Frame07" ref="A1:E93" totalsRowShown="0">
   <autoFilter ref="A1:E93" xr:uid="{195649B8-8D0B-4522-AC0C-8B85A3A56063}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D452DDE8-2CF6-446E-A4F9-D820195B59F3}" name="Year:" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{D2BFA669-97B8-4863-8EEB-2DC0D54A1BEB}" name="Historical" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{D452DDE8-2CF6-446E-A4F9-D820195B59F3}" name="Year:" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{D2BFA669-97B8-4863-8EEB-2DC0D54A1BEB}" name="Historical" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{A4410D91-46C3-4933-93B9-3589CE6C5ED0}" name="Median"/>
     <tableColumn id="4" xr3:uid="{A212DB55-74B7-4C6F-8DE9-7F64D74C8FED}" name="P05 Projected"/>
     <tableColumn id="5" xr3:uid="{7371A724-730E-4956-918D-7F6EDD168182}" name="P95 Projected"/>

--- a/MortalityExcel.xlsx
+++ b/MortalityExcel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My PC (DESKTOP-JQBDP5S)\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DB71CA2-B701-48F7-8C4D-3B0E12787AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9537515-73F1-420A-BAFF-8731A067FF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="15915" windowWidth="27960" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="15915" windowWidth="27960" windowHeight="16440" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Female Historical" sheetId="1" r:id="rId1"/>
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -126,12 +126,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="16">
-    <dxf>
-      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
     </dxf>
@@ -173,6 +167,12 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="#,##0.000;[Red]\-#,##0.000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -11820,8 +11820,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Frame0" displayName="Frame0" ref="A1:B93" totalsRowShown="0">
   <autoFilter ref="A1:B93" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year:" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="k_t" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year:" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="k_t" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11831,10 +11831,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Frame2" displayName="Frame2" ref="A1:D21" totalsRowShown="0">
   <autoFilter ref="A1:D21" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Year" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Median" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="P05" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="P95" dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Year" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Median" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="P05" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="P95" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11844,8 +11844,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{195649B8-8D0B-4522-AC0C-8B85A3A56063}" name="Frame07" displayName="Frame07" ref="A1:E93" totalsRowShown="0">
   <autoFilter ref="A1:E93" xr:uid="{195649B8-8D0B-4522-AC0C-8B85A3A56063}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D452DDE8-2CF6-446E-A4F9-D820195B59F3}" name="Year:" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{D2BFA669-97B8-4863-8EEB-2DC0D54A1BEB}" name="Historical" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{D452DDE8-2CF6-446E-A4F9-D820195B59F3}" name="Year:" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{D2BFA669-97B8-4863-8EEB-2DC0D54A1BEB}" name="Historical" dataDxfId="6"/>
     <tableColumn id="3" xr3:uid="{A4410D91-46C3-4933-93B9-3589CE6C5ED0}" name="Median"/>
     <tableColumn id="4" xr3:uid="{A212DB55-74B7-4C6F-8DE9-7F64D74C8FED}" name="P05 Projected"/>
     <tableColumn id="5" xr3:uid="{7371A724-730E-4956-918D-7F6EDD168182}" name="P95 Projected"/>
@@ -11858,8 +11858,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Frame1" displayName="Frame1" ref="A1:B93" totalsRowShown="0">
   <autoFilter ref="A1:B93" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Year:" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="k_t" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Year:" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="k_t" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11869,10 +11869,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Frame3" displayName="Frame3" ref="A1:D21" totalsRowShown="0">
   <autoFilter ref="A1:D21" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Year" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Median" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="P05" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="P95" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Year" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Median" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="P05" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="P95" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -11882,8 +11882,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4EA9706A-B69C-47D9-9690-9C84BF1310FE}" name="Frame16" displayName="Frame16" ref="A1:E113" totalsRowShown="0">
   <autoFilter ref="A1:E113" xr:uid="{4EA9706A-B69C-47D9-9690-9C84BF1310FE}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{D07CE5DA-38CC-49B0-96AB-D0E068147ED1}" name="Year:" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{9435D52C-767A-4344-B263-9120546BB3B8}" name="k_t" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{D07CE5DA-38CC-49B0-96AB-D0E068147ED1}" name="Year:" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{9435D52C-767A-4344-B263-9120546BB3B8}" name="k_t" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{6A3D2032-395C-48B2-A9EA-099822BEC295}" name="Median"/>
     <tableColumn id="4" xr3:uid="{9DBE78B3-F18E-4191-927C-293EE033DF1B}" name="P05 Projected"/>
     <tableColumn id="5" xr3:uid="{EFFE7BB2-FD43-4DAD-A6B0-317962C2BC1A}" name="P95 Projected"/>
